--- a/artfynd/A 23092-2020 artfynd.xlsx
+++ b/artfynd/A 23092-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 23092-2020 artfynd.xlsx
+++ b/artfynd/A 23092-2020 artfynd.xlsx
@@ -1190,7 +1190,7 @@
         <v>121278535</v>
       </c>
       <c r="B6" t="n">
-        <v>95618</v>
+        <v>95628</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 23092-2020 artfynd.xlsx
+++ b/artfynd/A 23092-2020 artfynd.xlsx
@@ -1292,7 +1292,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Johan Engström, Jonatan Strandberg</t>
+          <t>Jonatan Strandberg, Johan Engström</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">

--- a/artfynd/A 23092-2020 artfynd.xlsx
+++ b/artfynd/A 23092-2020 artfynd.xlsx
@@ -1190,7 +1190,7 @@
         <v>121278535</v>
       </c>
       <c r="B6" t="n">
-        <v>95628</v>
+        <v>95641</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Jonatan Strandberg, Johan Engström</t>
+          <t>Johan Engström, Jonatan Strandberg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">

--- a/artfynd/A 23092-2020 artfynd.xlsx
+++ b/artfynd/A 23092-2020 artfynd.xlsx
@@ -1190,7 +1190,7 @@
         <v>121278535</v>
       </c>
       <c r="B6" t="n">
-        <v>95641</v>
+        <v>95642</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 23092-2020 artfynd.xlsx
+++ b/artfynd/A 23092-2020 artfynd.xlsx
@@ -1190,7 +1190,7 @@
         <v>121278535</v>
       </c>
       <c r="B6" t="n">
-        <v>95642</v>
+        <v>95645</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 23092-2020 artfynd.xlsx
+++ b/artfynd/A 23092-2020 artfynd.xlsx
@@ -1190,7 +1190,7 @@
         <v>121278535</v>
       </c>
       <c r="B6" t="n">
-        <v>95645</v>
+        <v>95651</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Johan Engström, Jonatan Strandberg</t>
+          <t>Jonatan Strandberg, Johan Engström</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">

--- a/artfynd/A 23092-2020 artfynd.xlsx
+++ b/artfynd/A 23092-2020 artfynd.xlsx
@@ -1190,7 +1190,7 @@
         <v>121278535</v>
       </c>
       <c r="B6" t="n">
-        <v>95651</v>
+        <v>95652</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Jonatan Strandberg, Johan Engström</t>
+          <t>Johan Engström, Jonatan Strandberg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">

--- a/artfynd/A 23092-2020 artfynd.xlsx
+++ b/artfynd/A 23092-2020 artfynd.xlsx
@@ -1292,7 +1292,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Jonatan Strandberg, Johan Engström</t>
+          <t>Johan Engström, Jonatan Strandberg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
